--- a/WorkFlow Genie/backend/data/excel_files/9270c07d-e166-4d65-ae33-8c0012fdbf2c_students.xlsx
+++ b/WorkFlow Genie/backend/data/excel_files/9270c07d-e166-4d65-ae33-8c0012fdbf2c_students.xlsx
@@ -1,136 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9633e64aefc3f432/Dokumen/GitHub/WorkflowGenie-AI-For-Office-Automation/WorkFlow Genie/backend/data/excel_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D869872B-3933-4D2B-B557-7D50194D853C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{61D1B584-377F-40E0-8D73-84F326521742}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Roll No</t>
-  </si>
-  <si>
-    <t>Maths</t>
-  </si>
-  <si>
-    <t>Physics</t>
-  </si>
-  <si>
-    <t>Chem</t>
-  </si>
-  <si>
-    <t>Mustafa</t>
-  </si>
-  <si>
-    <t>Ali Yahya</t>
-  </si>
-  <si>
-    <t>Abdullah</t>
-  </si>
-  <si>
-    <t>Ansab</t>
-  </si>
-  <si>
-    <t>Nawfal</t>
-  </si>
-  <si>
-    <t>Alyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taha </t>
-  </si>
-  <si>
-    <t>Ali Soban</t>
-  </si>
-  <si>
-    <t>Samroze</t>
-  </si>
-  <si>
-    <t>22k-4166</t>
-  </si>
-  <si>
-    <t>22k-4417</t>
-  </si>
-  <si>
-    <t>22k-4147</t>
-  </si>
-  <si>
-    <t>22k-4520</t>
-  </si>
-  <si>
-    <t>22k-4372</t>
-  </si>
-  <si>
-    <t>22k-4582</t>
-  </si>
-  <si>
-    <t>22k-4144</t>
-  </si>
-  <si>
-    <t>22k-4353</t>
-  </si>
-  <si>
-    <t>22k-4187</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -149,22 +54,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -484,182 +448,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC67E37-1687-466B-A3D3-2FCB987C48CA}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Roll No</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>maths</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>maths</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mustafa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22k-4166</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>67</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>72</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ali Yahya</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>22k-4417</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>92</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>88</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Abdullah</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22k-4147</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>45</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>52</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ansab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22k-4520</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>78</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>82</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nawfal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>22k-4372</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>88</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>85</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alyan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22k-4582</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>55</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>60</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taha </t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22k-4144</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>95</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>92</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ali Soban</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22k-4353</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>72</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>68</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Samroze</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22k-4187</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>82</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>79</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>